--- a/architecture/IdentityCertificatesAndAuthentications/ArchitectureDesignAndAuditDocs/FrontEnd_DB_Analysis_2026-08-07.xlsx
+++ b/architecture/IdentityCertificatesAndAuthentications/ArchitectureDesignAndAuditDocs/FrontEnd_DB_Analysis_2026-08-07.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Front-end runtime only: sharedServices/, FindCare/, evaluateCare/, Code/ConversationalUX/FindCareChat/backend/, FrontEndApplicationLib/src/</t>
+          <t>Front-end runtime only: sharedServices/, FindCare/, evaluateCare/, Code/ConversationalUX/FindCareChat/backend/, ChatHealthyLib/src/</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Library (chathealthy-frontend-lib)</t>
+          <t>Library (chathealthy-lib)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/logging_service.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/logging_service.py</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Library (chathealthy-frontend-lib)</t>
+          <t>Library (chathealthy-lib)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/mongo_utilities.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/mongo_utilities.py</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>getConnection(role, cluster) at line 317 is the canonical connection factory used by every front-end Mongo call site - the file is unambiguously LIVE. DEAD paths inside it: _fetch_certs_and_uri (line 377) reads ChatHealthyConfig.CertificateRegistry at line 435, and _lookup_vault_key (line 541) reads the same collection at line 567. getConnection does NOT call either - it goes straight to os.environ[MONGO_FRONTEND_connectionString] and MongoClient (lines 357-369), despite the class docstring describing an X.509/vault flow. Searched the entire repo (excluding .venv, site-packages, build/, localBuild/, remoteBuild/, __pycache__) for _fetch_certs_and_uri, _lookup_vault_key, _build_mtls_uri, _create_mtls_client, _verify_cert_subject_cn, _extract_certificate_from_pem and for 'CertificateRegistry'. The only caller found anywhere is FrontEndApplicationLib/tests/test_logging_mongo.py:52 (_fetch_certs_and_uri). No runtime caller, no string dispatch, no importlib/getattr reference. _extract_certificate_from_pem is called only by _verify_cert_subject_cn (line 610), which itself has no caller.</t>
+          <t>getConnection(role, cluster) at line 317 is the canonical connection factory used by every front-end Mongo call site - the file is unambiguously LIVE. DEAD paths inside it: _fetch_certs_and_uri (line 377) reads ChatHealthyConfig.CertificateRegistry at line 435, and _lookup_vault_key (line 541) reads the same collection at line 567. getConnection does NOT call either - it goes straight to os.environ[MONGO_FRONTEND_connectionString] and MongoClient (lines 357-369), despite the class docstring describing an X.509/vault flow. Searched the entire repo (excluding .venv, site-packages, build/, localBuild/, remoteBuild/, __pycache__) for _fetch_certs_and_uri, _lookup_vault_key, _build_mtls_uri, _create_mtls_client, _verify_cert_subject_cn, _extract_certificate_from_pem and for 'CertificateRegistry'. The only caller found anywhere is ChatHealthyLib/tests/test_logging_mongo.py:52 (_fetch_certs_and_uri). No runtime caller, no string dispatch, no importlib/getattr reference. _extract_certificate_from_pem is called only by _verify_cert_subject_cn (line 610), which itself has no caller.</t>
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
@@ -2594,12 +2594,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Library (chathealthy-frontend-lib)</t>
+          <t>Library (chathealthy-lib)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/runtime_data_collections.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/runtime_data_collections.py</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3686,12 +3686,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Library (chathealthy-frontend-lib)</t>
+          <t>Library (chathealthy-lib)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FrontEndApplicationLib/src/chathealthy_frontend_lib/logging_service.py</t>
+          <t>ChatHealthyLib/src/chathealthy_lib/logging_service.py</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
